--- a/GMAX4651/РАСПИНОВКА_4651.xlsx
+++ b/GMAX4651/РАСПИНОВКА_4651.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1B03E4-BF42-45DF-B9EE-F676CED9BBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
   <si>
     <t>6581 A</t>
   </si>
@@ -202,12 +203,15 @@
   </si>
   <si>
     <t>3,3V_LVDS</t>
+  </si>
+  <si>
+    <t>OUTT0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -260,14 +264,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -563,22 +567,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="3" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="3"/>
+      <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -587,20 +591,20 @@
       <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="1">
         <v>0</v>
       </c>
@@ -615,16 +619,16 @@
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1">
         <v>1</v>
       </c>
@@ -639,16 +643,16 @@
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="1">
         <v>2</v>
       </c>
@@ -663,16 +667,16 @@
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -681,20 +685,20 @@
       <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="3" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -703,16 +707,16 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="1">
         <v>0</v>
       </c>
@@ -727,16 +731,16 @@
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="1">
         <v>1</v>
       </c>
@@ -751,16 +755,16 @@
       <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="1">
         <v>2</v>
       </c>
@@ -769,8 +773,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -779,24 +783,24 @@
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="3" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -805,16 +809,16 @@
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="1">
         <v>0</v>
       </c>
@@ -829,16 +833,16 @@
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="1">
         <v>1</v>
       </c>
@@ -853,16 +857,16 @@
       <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="1">
         <v>2</v>
       </c>
@@ -877,16 +881,16 @@
       <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -895,20 +899,20 @@
       <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
       <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="3" t="s">
+      <c r="G16" s="4"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="3"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -917,16 +921,16 @@
       <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="3"/>
       <c r="I17" s="1">
         <v>0</v>
       </c>
@@ -941,16 +945,16 @@
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="3"/>
       <c r="I18" s="1">
         <v>1</v>
       </c>
@@ -959,8 +963,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="1">
         <v>2</v>
       </c>
@@ -973,20 +977,20 @@
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="3"/>
       <c r="E20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="4"/>
+      <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -995,16 +999,16 @@
       <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1013,34 +1017,34 @@
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3"/>
       <c r="E22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="3"/>
       <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1049,16 +1053,16 @@
       <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="3"/>
       <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1067,16 +1071,16 @@
       <c r="B25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="3"/>
       <c r="E25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1085,16 +1089,16 @@
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3"/>
       <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1103,20 +1107,20 @@
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="3"/>
       <c r="E27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="D28" s="3"/>
+      <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1125,20 +1129,20 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="3"/>
       <c r="E29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1147,16 +1151,16 @@
       <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="3"/>
       <c r="E30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1165,33 +1169,33 @@
       <c r="B31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3"/>
       <c r="E31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C2:C9"/>
+    <mergeCell ref="C11:C18"/>
+    <mergeCell ref="G2:G9"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C20:C27"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="G29:G31"/>
     <mergeCell ref="G20:G27"/>
     <mergeCell ref="G11:G18"/>
-    <mergeCell ref="G2:G9"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C2:C9"/>
-    <mergeCell ref="C11:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/GMAX4651/РАСПИНОВКА_4651.xlsx
+++ b/GMAX4651/РАСПИНОВКА_4651.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1B03E4-BF42-45DF-B9EE-F676CED9BBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -211,7 +210,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -267,11 +266,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,37 +551,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.28515625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9.140625" style="1"/>
+    <col min="5" max="5" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -591,7 +592,7 @@
       <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="3"/>
@@ -601,7 +602,7 @@
       <c r="F2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>36</v>
       </c>
       <c r="H2" s="3"/>
@@ -619,7 +620,7 @@
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -627,7 +628,7 @@
       <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1">
         <v>1</v>
@@ -643,7 +644,7 @@
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1" t="s">
         <v>4</v>
@@ -651,7 +652,7 @@
       <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="5"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1">
         <v>2</v>
@@ -667,7 +668,7 @@
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1" t="s">
         <v>5</v>
@@ -675,7 +676,7 @@
       <c r="F5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -685,7 +686,7 @@
       <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1" t="s">
         <v>6</v>
@@ -693,12 +694,12 @@
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="5"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -707,7 +708,7 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1" t="s">
         <v>7</v>
@@ -715,7 +716,7 @@
       <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="5"/>
       <c r="H7" s="3"/>
       <c r="I7" s="1">
         <v>0</v>
@@ -731,7 +732,7 @@
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -739,7 +740,7 @@
       <c r="F8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="5"/>
       <c r="H8" s="3"/>
       <c r="I8" s="1">
         <v>1</v>
@@ -755,7 +756,7 @@
       <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1" t="s">
         <v>9</v>
@@ -763,7 +764,7 @@
       <c r="F9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="5"/>
       <c r="H9" s="3"/>
       <c r="I9" s="1">
         <v>2</v>
@@ -783,7 +784,7 @@
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="3"/>
@@ -793,14 +794,14 @@
       <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -809,7 +810,7 @@
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="3"/>
       <c r="E12" s="1" t="s">
         <v>11</v>
@@ -817,7 +818,7 @@
       <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="3"/>
       <c r="I12" s="1">
         <v>0</v>
@@ -833,7 +834,7 @@
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="3"/>
       <c r="E13" s="1" t="s">
         <v>12</v>
@@ -841,7 +842,7 @@
       <c r="F13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="5"/>
       <c r="H13" s="3"/>
       <c r="I13" s="1">
         <v>1</v>
@@ -857,7 +858,7 @@
       <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="3"/>
       <c r="E14" s="1" t="s">
         <v>13</v>
@@ -865,7 +866,7 @@
       <c r="F14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="3"/>
       <c r="I14" s="1">
         <v>2</v>
@@ -881,7 +882,7 @@
       <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -889,7 +890,7 @@
       <c r="F15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="5"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -899,7 +900,7 @@
       <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1" t="s">
         <v>15</v>
@@ -907,12 +908,12 @@
       <c r="F16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="5"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -921,7 +922,7 @@
       <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1" t="s">
         <v>16</v>
@@ -929,7 +930,7 @@
       <c r="F17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="4"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="3"/>
       <c r="I17" s="1">
         <v>0</v>
@@ -945,7 +946,7 @@
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="3"/>
       <c r="E18" s="1" t="s">
         <v>17</v>
@@ -953,7 +954,7 @@
       <c r="F18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="5"/>
       <c r="H18" s="3"/>
       <c r="I18" s="1">
         <v>1</v>
@@ -977,7 +978,7 @@
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D20" s="3"/>
@@ -987,7 +988,7 @@
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>36</v>
       </c>
       <c r="H20" s="3"/>
@@ -999,7 +1000,7 @@
       <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="3"/>
       <c r="E21" s="1" t="s">
         <v>19</v>
@@ -1007,7 +1008,7 @@
       <c r="F21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="4"/>
+      <c r="G21" s="5"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1017,7 +1018,7 @@
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="3"/>
       <c r="E22" s="1" t="s">
         <v>20</v>
@@ -1025,7 +1026,7 @@
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="4"/>
+      <c r="G22" s="5"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1035,7 +1036,7 @@
       <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="3"/>
       <c r="E23" s="1" t="s">
         <v>21</v>
@@ -1043,7 +1044,7 @@
       <c r="F23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="4"/>
+      <c r="G23" s="5"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1053,7 +1054,7 @@
       <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="3"/>
       <c r="E24" s="1" t="s">
         <v>22</v>
@@ -1061,7 +1062,7 @@
       <c r="F24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G24" s="4"/>
+      <c r="G24" s="5"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1071,7 +1072,7 @@
       <c r="B25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="3"/>
       <c r="E25" s="1" t="s">
         <v>23</v>
@@ -1079,7 +1080,7 @@
       <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="4"/>
+      <c r="G25" s="5"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1089,7 +1090,7 @@
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="3"/>
       <c r="E26" s="1" t="s">
         <v>24</v>
@@ -1097,7 +1098,7 @@
       <c r="F26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="4"/>
+      <c r="G26" s="5"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1107,7 +1108,7 @@
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="3"/>
       <c r="E27" s="1" t="s">
         <v>25</v>
@@ -1115,7 +1116,7 @@
       <c r="F27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="4"/>
+      <c r="G27" s="5"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1129,7 +1130,7 @@
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D29" s="3"/>
@@ -1139,7 +1140,7 @@
       <c r="F29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="3"/>
@@ -1151,7 +1152,7 @@
       <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="4"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="3"/>
       <c r="E30" s="1" t="s">
         <v>27</v>
@@ -1159,7 +1160,7 @@
       <c r="F30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="4"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1169,7 +1170,7 @@
       <c r="B31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="4"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="3"/>
       <c r="E31" s="1" t="s">
         <v>28</v>
@@ -1177,25 +1178,25 @@
       <c r="F31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="4"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="G20:G27"/>
+    <mergeCell ref="G11:G18"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C20:C27"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="C2:C9"/>
     <mergeCell ref="C11:C18"/>
     <mergeCell ref="G2:G9"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="G20:G27"/>
-    <mergeCell ref="G11:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
